--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="D3">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>1</v>
